--- a/data/trans_orig/Q20C_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q20C_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo de espera en meses para ser hospitalizado (cuartiles) en 2007</t>
+          <t>Población según el tiempo de espera en meses para ser hospitalizado (cuartiles) en 2007 (tasa de respuesta: 96,63%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10128</t>
+          <t>10098</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3801</t>
+          <t>3719</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13577</t>
+          <t>12850</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8587</t>
+          <t>8338</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20901</t>
+          <t>19891</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>41,54%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4272</t>
+          <t>4355</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4539</t>
+          <t>4612</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13512</t>
+          <t>14206</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4785</t>
+          <t>4665</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15072</t>
+          <t>15588</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>32,55%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>933</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7378</t>
+          <t>7370</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4784</t>
+          <t>5394</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1804</t>
+          <t>1799</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9468</t>
+          <t>9990</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>20,86%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2797</t>
+          <t>3471</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10782</t>
+          <t>10548</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8367</t>
+          <t>8561</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19193</t>
+          <t>19048</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13456</t>
+          <t>13482</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26416</t>
+          <t>26059</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>54,42%</t>
         </is>
       </c>
     </row>
@@ -1302,97 +1302,97 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1601</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>4056</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>6,87%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>20,75%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>28,5%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>977</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>4041</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>6,87%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>4776</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>4,45%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>28,39%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>4966</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>4,45%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>21,76%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5041</t>
+          <t>3922</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5924</t>
+          <t>6585</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>931</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7210</t>
+          <t>7295</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>33,24%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>987</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5941</t>
+          <t>5924</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>772</t>
+          <t>516</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6638</t>
+          <t>6232</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>2641</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10555</t>
+          <t>10567</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>48,15%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>897</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>4953</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11676</t>
+          <t>12199</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7532</t>
+          <t>7723</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16701</t>
+          <t>17008</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>77,49%</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6106</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,62 +1906,62 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>2502</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>1491</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>7294</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>20,03%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>36,25%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>2502</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>7020</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>20,03%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>58,4%</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5433</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,62 +2019,62 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>2043</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>1491</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>5885</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>16,36%</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>36,25%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>2043</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>5423</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>16,36%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>47,13%</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4872</t>
+          <t>4462</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6165</t>
+          <t>5720</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>45,8%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>765</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6109</t>
+          <t>6149</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>2627</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9499</t>
+          <t>9370</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>75,03%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>4484</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14587</t>
+          <t>14136</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>4570</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14723</t>
+          <t>14833</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11208</t>
+          <t>11181</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>25061</t>
+          <t>26193</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>31,82%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>969</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8328</t>
+          <t>8325</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5783</t>
+          <t>5716</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16941</t>
+          <t>16648</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9268</t>
+          <t>8731</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>21822</t>
+          <t>21805</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,49%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3673</t>
+          <t>3516</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13196</t>
+          <t>13812</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>1747</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9432</t>
+          <t>9750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>7107</t>
+          <t>6959</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>20403</t>
+          <t>20247</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,59%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7529</t>
+          <t>7911</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18435</t>
+          <t>18635</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18396</t>
+          <t>19041</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32059</t>
+          <t>31956</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>29243</t>
+          <t>29500</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>46895</t>
+          <t>47277</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>57,43%</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo de espera en meses para ser hospitalizado (cuartiles) en 2012</t>
+          <t>Población según el tiempo de espera en meses para ser hospitalizado (cuartiles) en 2012 (tasa de respuesta: 97,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2064</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10645</t>
+          <t>11388</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4068</t>
+          <t>4099</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14574</t>
+          <t>14275</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7062</t>
+          <t>7303</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20673</t>
+          <t>21575</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>32,69%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11203</t>
+          <t>10939</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3244</t>
+          <t>3360</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13563</t>
+          <t>13794</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6530</t>
+          <t>6330</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20810</t>
+          <t>21215</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>32,15%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2873</t>
+          <t>2819</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12594</t>
+          <t>12519</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10542</t>
+          <t>10873</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6603</t>
+          <t>6578</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19388</t>
+          <t>19979</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>30,27%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6514</t>
+          <t>5996</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17216</t>
+          <t>16864</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10513</t>
+          <t>10805</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23705</t>
+          <t>23683</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20794</t>
+          <t>20034</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36745</t>
+          <t>36987</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>56,05%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2164</t>
+          <t>2230</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11217</t>
+          <t>11204</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4168</t>
+          <t>4292</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15383</t>
+          <t>15818</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>9132</t>
+          <t>8600</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>23850</t>
+          <t>23460</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>37,78%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2935</t>
+          <t>2952</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12430</t>
+          <t>12065</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1189</t>
+          <t>1163</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10947</t>
+          <t>10926</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6496</t>
+          <t>5966</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19755</t>
+          <t>19609</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,58%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2184</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10790</t>
+          <t>10618</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4883</t>
+          <t>4751</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16179</t>
+          <t>14924</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9159</t>
+          <t>8680</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>22777</t>
+          <t>21757</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>35,04%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4421</t>
+          <t>5224</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15509</t>
+          <t>15808</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5423</t>
+          <t>5584</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16994</t>
+          <t>16813</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13316</t>
+          <t>13205</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>28225</t>
+          <t>27731</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>44,66%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1760</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7834</t>
+          <t>7827</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8592</t>
+          <t>8516</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>70,23%</t>
         </is>
       </c>
     </row>
@@ -4491,97 +4491,97 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1067</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>1760</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>5048</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>11,81%</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>55,88%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="R15" s="2" t="inlineStr">
         <is>
           <t>1067</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="S15" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>4411</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>11,81%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>5935</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>8,8%</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>48,82%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>1067</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>4709</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>8,8%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>48,94%</t>
         </is>
       </c>
     </row>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5675</t>
+          <t>5725</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8592</t>
+          <t>8908</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>73,46%</t>
         </is>
       </c>
     </row>
@@ -4757,7 +4757,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5530</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>55,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6351</t>
+          <t>6721</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>55,42%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6444</t>
+          <t>6131</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18900</t>
+          <t>19556</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14580</t>
+          <t>14419</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30653</t>
+          <t>30731</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24401</t>
+          <t>23980</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>45049</t>
+          <t>43981</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>31,37%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5884</t>
+          <t>5890</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19238</t>
+          <t>19124</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7690</t>
+          <t>7894</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>22269</t>
+          <t>22023</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>16580</t>
+          <t>16269</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>36217</t>
+          <t>36677</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,16%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8582</t>
+          <t>8144</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>23755</t>
+          <t>23736</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>10210</t>
+          <t>10078</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>24749</t>
+          <t>24815</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>21767</t>
+          <t>21841</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>42598</t>
+          <t>43317</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,89%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14633</t>
+          <t>14537</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29421</t>
+          <t>29828</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19669</t>
+          <t>20309</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>38531</t>
+          <t>37746</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>39598</t>
+          <t>39559</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>63762</t>
+          <t>63321</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>45,16%</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo de espera en meses para ser hospitalizado (cuartiles) en 2016</t>
+          <t>Población según el tiempo de espera en meses para ser hospitalizado (cuartiles) en 2016 (tasa de respuesta: 92,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5752,7 +5752,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4425</t>
+          <t>5120</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1704</t>
+          <t>1665</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9382</t>
+          <t>9430</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11552</t>
+          <t>11126</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>29,48%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>753</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6912</t>
+          <t>6792</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2087</t>
+          <t>1938</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11012</t>
+          <t>10837</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4066</t>
+          <t>4050</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14042</t>
+          <t>14470</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>38,35%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2851</t>
+          <t>2801</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9796</t>
+          <t>9754</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5774</t>
+          <t>5724</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3543</t>
+          <t>3967</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13592</t>
+          <t>14090</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>37,34%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>787</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6714</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7352</t>
+          <t>7454</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17923</t>
+          <t>17957</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9557</t>
+          <t>9921</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21964</t>
+          <t>22747</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>60,28%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5345</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>16904</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5410</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17013</t>
+          <t>17424</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>13837</t>
+          <t>13768</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>29628</t>
+          <t>30593</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>45,36%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3830</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14788</t>
+          <t>14916</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16087</t>
+          <t>15654</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10649</t>
+          <t>10759</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26605</t>
+          <t>27381</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>40,6%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3465</t>
+          <t>3919</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13843</t>
+          <t>14298</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1597</t>
+          <t>1574</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11341</t>
+          <t>10962</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7540</t>
+          <t>7186</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>22532</t>
+          <t>21060</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>31,23%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>3304</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12898</t>
+          <t>13725</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3238</t>
+          <t>3875</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13734</t>
+          <t>14162</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8265</t>
+          <t>8747</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>22247</t>
+          <t>22984</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>34,08%</t>
         </is>
       </c>
     </row>
@@ -6885,97 +6885,97 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1572</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>36,25%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>1148</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1678</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7073,7 +7073,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4865</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>82,11%</t>
         </is>
       </c>
     </row>
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6353</t>
+          <t>5537</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>87,16%</t>
         </is>
       </c>
     </row>
@@ -7229,7 +7229,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3337</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,62 +7259,62 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>964</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>1148</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>4228</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>15,17%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>964</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>4227</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>15,17%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,56%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6087</t>
+          <t>5778</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19857</t>
+          <t>18392</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>9300</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23784</t>
+          <t>23282</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18642</t>
+          <t>19332</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>37453</t>
+          <t>38315</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>34,35%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6327</t>
+          <t>6834</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18504</t>
+          <t>19544</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9985</t>
+          <t>9333</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>24359</t>
+          <t>24998</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>18899</t>
+          <t>19716</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>38555</t>
+          <t>39251</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>35,19%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10501</t>
+          <t>9867</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>24247</t>
+          <t>23872</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3472</t>
+          <t>3142</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15046</t>
+          <t>15136</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>16727</t>
+          <t>16788</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>35245</t>
+          <t>34781</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,19%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6608</t>
+          <t>6113</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18981</t>
+          <t>18609</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12774</t>
+          <t>13225</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29028</t>
+          <t>29107</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>22579</t>
+          <t>22528</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>42491</t>
+          <t>42242</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>37,88%</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo de espera en meses para ser hospitalizado (cuartiles) en 2023</t>
+          <t>Población según el tiempo de espera en meses para ser hospitalizado (cuartiles) en 2023 (tasa de respuesta: 93,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2524</t>
+          <t>2480</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8812</t>
+          <t>8766</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8269,12 +8269,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>318</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3272</t>
+          <t>3510</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3781</t>
+          <t>3638</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10992</t>
+          <t>10451</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>36,84%</t>
         </is>
       </c>
     </row>
@@ -8367,12 +8367,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5956</t>
+          <t>5625</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8402,12 +8402,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2859</t>
+          <t>2647</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7884</t>
+          <t>7902</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8437,12 +8437,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4326</t>
+          <t>4787</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11594</t>
+          <t>11805</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>41,61%</t>
         </is>
       </c>
     </row>
@@ -8485,7 +8485,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2743</t>
+          <t>3054</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8500,7 +8500,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>516</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5198</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8550,12 +8550,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>764</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5680</t>
+          <t>5676</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,01%</t>
         </is>
       </c>
     </row>
@@ -8593,12 +8593,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3295</t>
+          <t>3351</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10216</t>
+          <t>10272</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8608,12 +8608,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2266</t>
+          <t>2223</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7109</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7615</t>
+          <t>7732</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15672</t>
+          <t>15998</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>56,38%</t>
         </is>
       </c>
     </row>
@@ -8823,12 +8823,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3053</t>
+          <t>2827</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12300</t>
+          <t>11830</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8838,12 +8838,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2280</t>
+          <t>2378</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8806</t>
+          <t>8943</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7184</t>
+          <t>7605</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>18247</t>
+          <t>18356</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,68%</t>
         </is>
       </c>
     </row>
@@ -8936,12 +8936,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1628</t>
+          <t>1811</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8148</t>
+          <t>8648</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1460</t>
+          <t>1537</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7064</t>
+          <t>7345</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4398</t>
+          <t>4451</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12602</t>
+          <t>12812</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,51%</t>
         </is>
       </c>
     </row>
@@ -9049,12 +9049,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2768</t>
+          <t>2461</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10667</t>
+          <t>10990</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9064,12 +9064,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9084,12 +9084,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1580</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7359</t>
+          <t>7197</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9099,12 +9099,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9119,12 +9119,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5139</t>
+          <t>5075</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>15771</t>
+          <t>14734</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9134,12 +9134,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>27,04%</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8270</t>
+          <t>8687</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18807</t>
+          <t>19509</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7116</t>
+          <t>7443</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15281</t>
+          <t>15318</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>18419</t>
+          <t>17486</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>32231</t>
+          <t>31290</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9247,12 +9247,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>57,42%</t>
         </is>
       </c>
     </row>
@@ -9397,7 +9397,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6094</t>
+          <t>5700</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9412,7 +9412,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>382</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4247</t>
+          <t>3974</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>1632</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8080</t>
+          <t>7930</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>44,86%</t>
         </is>
       </c>
     </row>
@@ -9510,7 +9510,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4400</t>
+          <t>4028</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9525,7 +9525,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9545,7 +9545,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3361</t>
+          <t>3070</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9560,7 +9560,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>179</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6461</t>
+          <t>5708</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9590,12 +9590,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>32,3%</t>
         </is>
       </c>
     </row>
@@ -9618,12 +9618,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2448</t>
+          <t>2711</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9108</t>
+          <t>8991</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9633,12 +9633,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2222</t>
+          <t>2431</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9673,7 +9673,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2974</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11033</t>
+          <t>11605</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9703,12 +9703,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>65,66%</t>
         </is>
       </c>
     </row>
@@ -9736,7 +9736,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4707</t>
+          <t>4175</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9751,7 +9751,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1864</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5891</t>
+          <t>5924</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9801,12 +9801,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2431</t>
+          <t>2367</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9074</t>
+          <t>9232</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9816,12 +9816,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>52,23%</t>
         </is>
       </c>
     </row>
@@ -9961,12 +9961,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9714</t>
+          <t>9372</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22730</t>
+          <t>21865</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5266</t>
+          <t>4885</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12741</t>
+          <t>12820</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10011,12 +10011,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16301</t>
+          <t>16303</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30760</t>
+          <t>31186</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10051,7 +10051,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>31,02%</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4255</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14513</t>
+          <t>13842</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6300</t>
+          <t>5923</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14441</t>
+          <t>14249</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12388</t>
+          <t>12278</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>25050</t>
+          <t>24325</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10159,12 +10159,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,19%</t>
         </is>
       </c>
     </row>
@@ -10187,12 +10187,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6988</t>
+          <t>7038</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19730</t>
+          <t>19769</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3180</t>
+          <t>3095</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10388</t>
+          <t>10418</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10237,12 +10237,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>12045</t>
+          <t>11970</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>26772</t>
+          <t>27183</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>27,04%</t>
         </is>
       </c>
     </row>
@@ -10300,12 +10300,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14436</t>
+          <t>15105</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28552</t>
+          <t>29300</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10315,12 +10315,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14729</t>
+          <t>14757</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25210</t>
+          <t>25251</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32014</t>
+          <t>32708</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>50420</t>
+          <t>49863</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10385,12 +10385,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>49,59%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q20C_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q20C_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2774</t>
+          <t>2798</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10098</t>
+          <t>10749</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>3741</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12850</t>
+          <t>12768</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8338</t>
+          <t>8402</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19891</t>
+          <t>20616</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>43,05%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4355</t>
+          <t>3497</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4612</t>
+          <t>4571</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14206</t>
+          <t>13922</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4665</t>
+          <t>4678</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15588</t>
+          <t>15672</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,73%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>972</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7370</t>
+          <t>7511</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5394</t>
+          <t>3962</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1799</t>
+          <t>1739</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9990</t>
+          <t>9351</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>19,53%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3471</t>
+          <t>2737</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10548</t>
+          <t>10782</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8561</t>
+          <t>8395</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19048</t>
+          <t>18715</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13482</t>
+          <t>13937</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26059</t>
+          <t>26859</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>56,09%</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4056</t>
+          <t>4670</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4776</t>
+          <t>4878</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>22,23%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>3868</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6585</t>
+          <t>6809</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>935</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7295</t>
+          <t>7820</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>35,63%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5924</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>776</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>6190</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2641</t>
+          <t>2563</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10567</t>
+          <t>10234</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>46,63%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>910</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4953</t>
+          <t>4876</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12199</t>
+          <t>11608</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7723</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17008</t>
+          <t>16246</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>74,02%</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>6068</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7294</t>
+          <t>6527</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>52,27%</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5425</t>
+          <t>5399</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>5885</t>
+          <t>5469</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>43,8%</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4462</t>
+          <t>4423</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5720</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>47,28%</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6149</t>
+          <t>6144</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2627</t>
+          <t>2177</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9370</t>
+          <t>9395</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>75,23%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4484</t>
+          <t>4492</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14136</t>
+          <t>14910</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4570</t>
+          <t>4076</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14833</t>
+          <t>14980</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11181</t>
+          <t>10902</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26193</t>
+          <t>25698</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,22%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>959</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8325</t>
+          <t>8606</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5716</t>
+          <t>5528</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16648</t>
+          <t>17066</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8731</t>
+          <t>8323</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>21805</t>
+          <t>22150</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,91%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3516</t>
+          <t>3909</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13812</t>
+          <t>13624</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1747</t>
+          <t>1732</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9750</t>
+          <t>9407</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6959</t>
+          <t>7368</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>20247</t>
+          <t>20284</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,64%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7911</t>
+          <t>7805</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18635</t>
+          <t>18611</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19041</t>
+          <t>18531</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31956</t>
+          <t>32063</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>29500</t>
+          <t>29465</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>47277</t>
+          <t>46883</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>56,95%</t>
         </is>
       </c>
     </row>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11388</t>
+          <t>10488</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4099</t>
+          <t>3968</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14275</t>
+          <t>14072</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7303</t>
+          <t>8101</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21575</t>
+          <t>21296</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,27%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10939</t>
+          <t>10921</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3360</t>
+          <t>3146</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13794</t>
+          <t>13292</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6330</t>
+          <t>6295</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21215</t>
+          <t>19894</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>30,15%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2819</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12519</t>
+          <t>12161</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10873</t>
+          <t>10771</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6578</t>
+          <t>6934</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19979</t>
+          <t>20510</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>31,08%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5996</t>
+          <t>6584</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16864</t>
+          <t>16858</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10805</t>
+          <t>11068</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23683</t>
+          <t>23312</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20034</t>
+          <t>20621</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36987</t>
+          <t>37159</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>56,05%</t>
+          <t>56,31%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2230</t>
+          <t>2802</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11204</t>
+          <t>11421</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4292</t>
+          <t>4181</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15818</t>
+          <t>15155</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>8600</t>
+          <t>8702</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>23460</t>
+          <t>22441</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>36,14%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2952</t>
+          <t>2960</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12065</t>
+          <t>11702</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10926</t>
+          <t>11030</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5966</t>
+          <t>6503</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19609</t>
+          <t>20477</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>32,98%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>2507</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10618</t>
+          <t>10557</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4751</t>
+          <t>4537</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14924</t>
+          <t>14801</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8680</t>
+          <t>8838</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>21757</t>
+          <t>22083</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,56%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>4699</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15808</t>
+          <t>14770</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5584</t>
+          <t>5529</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16813</t>
+          <t>16550</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13205</t>
+          <t>13287</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>27731</t>
+          <t>28585</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>46,03%</t>
         </is>
       </c>
     </row>
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>1183</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7827</t>
+          <t>7674</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8516</t>
+          <t>8670</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>71,5%</t>
         </is>
       </c>
     </row>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>5935</t>
+          <t>4903</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>40,43%</t>
         </is>
       </c>
     </row>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5725</t>
+          <t>5767</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8908</t>
+          <t>8778</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>72,39%</t>
         </is>
       </c>
     </row>
@@ -4757,7 +4757,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5021</t>
+          <t>5023</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6721</t>
+          <t>6323</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>52,15%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6131</t>
+          <t>6350</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19556</t>
+          <t>18818</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14419</t>
+          <t>14137</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30731</t>
+          <t>30575</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23980</t>
+          <t>23883</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>43981</t>
+          <t>44615</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,82%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5890</t>
+          <t>5774</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19124</t>
+          <t>18516</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7894</t>
+          <t>7048</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>22023</t>
+          <t>21196</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>16269</t>
+          <t>16695</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>36677</t>
+          <t>35253</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>25,14%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8144</t>
+          <t>8553</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>23736</t>
+          <t>23323</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>10078</t>
+          <t>10220</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>24815</t>
+          <t>25295</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>21841</t>
+          <t>21642</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>43317</t>
+          <t>42416</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,25%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14537</t>
+          <t>14468</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29828</t>
+          <t>30166</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>51,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20309</t>
+          <t>19705</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>37746</t>
+          <t>38885</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>39559</t>
+          <t>39397</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>63321</t>
+          <t>63446</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>45,25%</t>
         </is>
       </c>
     </row>
@@ -5752,7 +5752,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5120</t>
+          <t>5295</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1665</t>
+          <t>1766</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9430</t>
+          <t>9854</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1965</t>
+          <t>1976</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11126</t>
+          <t>11609</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>30,76%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>769</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6792</t>
+          <t>6892</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1938</t>
+          <t>2091</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10837</t>
+          <t>10376</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>3441</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14470</t>
+          <t>14072</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>37,29%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2801</t>
+          <t>2743</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9754</t>
+          <t>9770</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5724</t>
+          <t>5869</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3967</t>
+          <t>3617</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14090</t>
+          <t>13523</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>35,84%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>824</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>6819</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7454</t>
+          <t>7351</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17957</t>
+          <t>17832</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>9614</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22747</t>
+          <t>22816</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>60,47%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5182</t>
+          <t>5039</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16904</t>
+          <t>17108</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>6109</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17424</t>
+          <t>18053</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>54,03%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>13768</t>
+          <t>14277</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>30593</t>
+          <t>30235</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>44,83%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>4015</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14916</t>
+          <t>14648</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>4100</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15654</t>
+          <t>15878</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10759</t>
+          <t>10631</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27381</t>
+          <t>25736</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>38,16%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3919</t>
+          <t>4008</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14298</t>
+          <t>14094</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1574</t>
+          <t>1456</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10962</t>
+          <t>10505</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7186</t>
+          <t>7660</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>21060</t>
+          <t>21035</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,19%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3304</t>
+          <t>3255</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13725</t>
+          <t>14090</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3875</t>
+          <t>3247</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14162</t>
+          <t>13353</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8747</t>
+          <t>9434</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>22984</t>
+          <t>22955</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>34,04%</t>
         </is>
       </c>
     </row>
@@ -7073,7 +7073,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>4384</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>69,0%</t>
         </is>
       </c>
     </row>
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5537</t>
+          <t>5608</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>88,27%</t>
         </is>
       </c>
     </row>
@@ -7229,7 +7229,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4022</t>
+          <t>4336</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4228</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>60,6%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5778</t>
+          <t>5647</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18392</t>
+          <t>18297</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9300</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23282</t>
+          <t>23513</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>19332</t>
+          <t>19221</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38315</t>
+          <t>37717</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>33,82%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6834</t>
+          <t>6457</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19544</t>
+          <t>19084</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9333</t>
+          <t>9788</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>24998</t>
+          <t>24095</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>19716</t>
+          <t>18968</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>39251</t>
+          <t>38804</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>34,79%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9867</t>
+          <t>10876</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>23872</t>
+          <t>24698</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>3465</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15136</t>
+          <t>16205</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>16788</t>
+          <t>17048</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>34781</t>
+          <t>34410</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>30,85%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6113</t>
+          <t>6552</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18609</t>
+          <t>18432</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13225</t>
+          <t>13005</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29107</t>
+          <t>29035</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>22528</t>
+          <t>21957</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>42242</t>
+          <t>41987</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,65%</t>
         </is>
       </c>
     </row>
@@ -8249,32 +8249,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5348</t>
+          <t>5473</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2480</t>
+          <t>2569</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8766</t>
+          <t>9140</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8284,32 +8284,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1363</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>352</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3510</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8319,32 +8319,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>6711</t>
+          <t>6867</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3638</t>
+          <t>3666</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10451</t>
+          <t>11269</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,98%</t>
         </is>
       </c>
     </row>
@@ -8362,32 +8362,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2785</t>
+          <t>2771</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>999</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5625</t>
+          <t>5851</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8397,32 +8397,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5160</t>
+          <t>5962</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2647</t>
+          <t>3165</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7902</t>
+          <t>8950</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8432,32 +8432,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>7945</t>
+          <t>8733</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4787</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11805</t>
+          <t>12861</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>42,21%</t>
         </is>
       </c>
     </row>
@@ -8475,7 +8475,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>586</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -8485,12 +8485,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3054</t>
+          <t>2725</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -8500,7 +8500,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8510,32 +8510,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1857</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>545</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4327</t>
+          <t>4977</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8545,32 +8545,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>2427</t>
+          <t>2926</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5676</t>
+          <t>6255</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,53%</t>
         </is>
       </c>
     </row>
@@ -8588,32 +8588,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6772</t>
+          <t>7140</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3351</t>
+          <t>3835</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10272</t>
+          <t>10734</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8623,32 +8623,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4518</t>
+          <t>4807</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2223</t>
+          <t>2482</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>7871</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8658,32 +8658,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>11290</t>
+          <t>11947</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7732</t>
+          <t>7812</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15998</t>
+          <t>16503</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>54,16%</t>
         </is>
       </c>
     </row>
@@ -8701,17 +8701,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>15476</t>
+          <t>15970</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15476</t>
+          <t>15970</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15476</t>
+          <t>15970</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8736,17 +8736,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>12897</t>
+          <t>14503</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12897</t>
+          <t>14503</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12897</t>
+          <t>14503</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8771,17 +8771,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>28373</t>
+          <t>30473</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>28373</t>
+          <t>30473</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>28373</t>
+          <t>30473</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8818,32 +8818,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>9853</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2827</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11830</t>
+          <t>15767</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8853,32 +8853,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>6538</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2378</t>
+          <t>3394</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8943</t>
+          <t>11303</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8888,32 +8888,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>12182</t>
+          <t>16391</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7605</t>
+          <t>10639</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>18356</t>
+          <t>23311</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>37,17%</t>
         </is>
       </c>
     </row>
@@ -8931,32 +8931,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4240</t>
+          <t>4170</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1811</t>
+          <t>1627</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8648</t>
+          <t>8703</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8966,32 +8966,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3681</t>
+          <t>4351</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1537</t>
+          <t>1850</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7345</t>
+          <t>8227</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9001,32 +9001,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>7921</t>
+          <t>8521</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4451</t>
+          <t>4745</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12812</t>
+          <t>14439</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,03%</t>
         </is>
       </c>
     </row>
@@ -9044,32 +9044,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5846</t>
+          <t>7056</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2461</t>
+          <t>3322</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10990</t>
+          <t>12644</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9079,32 +9079,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3764</t>
+          <t>3855</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>1619</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7197</t>
+          <t>7815</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9114,32 +9114,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>9610</t>
+          <t>10911</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5075</t>
+          <t>6339</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14734</t>
+          <t>17668</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>28,18%</t>
         </is>
       </c>
     </row>
@@ -9157,32 +9157,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13510</t>
+          <t>14319</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8687</t>
+          <t>8466</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19509</t>
+          <t>20537</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>58,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9192,32 +9192,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11272</t>
+          <t>12567</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7443</t>
+          <t>8045</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15318</t>
+          <t>17475</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9227,32 +9227,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>24782</t>
+          <t>26885</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>17486</t>
+          <t>19525</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>31290</t>
+          <t>34840</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>55,56%</t>
         </is>
       </c>
     </row>
@@ -9270,17 +9270,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>30543</t>
+          <t>35398</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30543</t>
+          <t>35398</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30543</t>
+          <t>35398</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9305,17 +9305,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>23952</t>
+          <t>27311</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23952</t>
+          <t>27311</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23952</t>
+          <t>27311</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9340,17 +9340,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>54496</t>
+          <t>62708</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54496</t>
+          <t>62708</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54496</t>
+          <t>62708</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9387,32 +9387,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2544</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>629</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>5896</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9422,32 +9422,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1690</t>
+          <t>2339</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>685</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3974</t>
+          <t>5093</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9457,32 +9457,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>4234</t>
+          <t>4788</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1632</t>
+          <t>2187</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7930</t>
+          <t>9146</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>46,23%</t>
         </is>
       </c>
     </row>
@@ -9500,7 +9500,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -9510,12 +9510,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4028</t>
+          <t>5404</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -9525,7 +9525,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9535,7 +9535,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>848</t>
+          <t>1413</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -9545,12 +9545,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3070</t>
+          <t>3857</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -9560,7 +9560,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9570,32 +9570,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>2488</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>661</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>5708</t>
+          <t>6068</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>30,67%</t>
         </is>
       </c>
     </row>
@@ -9613,32 +9613,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5774</t>
+          <t>6062</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2711</t>
+          <t>2669</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8991</t>
+          <t>9298</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>472</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -9658,12 +9658,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2431</t>
+          <t>2148</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -9673,7 +9673,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9683,32 +9683,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>6242</t>
+          <t>6534</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2809</t>
+          <t>2528</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11605</t>
+          <t>11930</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>60,3%</t>
         </is>
       </c>
     </row>
@@ -9726,7 +9726,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1603</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -9736,12 +9736,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4175</t>
+          <t>4832</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -9751,7 +9751,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9761,32 +9761,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3957</t>
+          <t>4372</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5924</t>
+          <t>6871</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9796,32 +9796,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5975</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2367</t>
+          <t>2613</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9232</t>
+          <t>10175</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>51,43%</t>
         </is>
       </c>
     </row>
@@ -9839,17 +9839,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>10712</t>
+          <t>11188</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10712</t>
+          <t>11188</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10712</t>
+          <t>11188</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9874,17 +9874,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>8596</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>8596</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>8596</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9909,17 +9909,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>17675</t>
+          <t>19784</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>17675</t>
+          <t>19784</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>17675</t>
+          <t>19784</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9956,32 +9956,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14839</t>
+          <t>17774</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9372</t>
+          <t>11824</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21865</t>
+          <t>25634</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9991,32 +9991,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8289</t>
+          <t>10272</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4885</t>
+          <t>6272</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12820</t>
+          <t>14935</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10026,32 +10026,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>23127</t>
+          <t>28046</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16303</t>
+          <t>20005</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31186</t>
+          <t>36486</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>32,3%</t>
         </is>
       </c>
     </row>
@@ -10069,32 +10069,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>8060</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4255</t>
+          <t>4019</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13842</t>
+          <t>13244</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10104,32 +10104,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>9688</t>
+          <t>11726</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5923</t>
+          <t>7555</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14249</t>
+          <t>17552</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10139,32 +10139,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>17748</t>
+          <t>19742</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12278</t>
+          <t>13585</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>24325</t>
+          <t>26517</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>23,47%</t>
         </is>
       </c>
     </row>
@@ -10182,32 +10182,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12190</t>
+          <t>13704</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7038</t>
+          <t>8162</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19769</t>
+          <t>21613</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10217,32 +10217,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6089</t>
+          <t>6667</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3095</t>
+          <t>3447</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10418</t>
+          <t>11298</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10252,32 +10252,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>18280</t>
+          <t>20370</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>11970</t>
+          <t>13852</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>27183</t>
+          <t>28885</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>25,57%</t>
         </is>
       </c>
     </row>
@@ -10295,32 +10295,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>21643</t>
+          <t>23061</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15105</t>
+          <t>16108</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29300</t>
+          <t>31417</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10330,32 +10330,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>19746</t>
+          <t>21746</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14757</t>
+          <t>16316</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25251</t>
+          <t>27791</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10365,32 +10365,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>41389</t>
+          <t>44807</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32708</t>
+          <t>35503</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>49863</t>
+          <t>54331</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>48,1%</t>
         </is>
       </c>
     </row>
@@ -10408,17 +10408,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>56732</t>
+          <t>62555</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>56732</t>
+          <t>62555</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>56732</t>
+          <t>62555</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10443,17 +10443,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>43812</t>
+          <t>50410</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>43812</t>
+          <t>50410</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>43812</t>
+          <t>50410</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10478,17 +10478,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>100544</t>
+          <t>112965</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>100544</t>
+          <t>112965</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>100544</t>
+          <t>112965</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
